--- a/commodity-risk-dashboard/data/commodities_powerbi.xlsx
+++ b/commodity-risk-dashboard/data/commodities_powerbi.xlsx
@@ -79550,34 +79550,34 @@
         <v>298.1499938964844</v>
       </c>
       <c r="E1515" t="n">
-        <v>318.0499877929688</v>
+        <v>324.3999938964844</v>
       </c>
       <c r="F1515" t="n">
         <v>311.3500061035156</v>
       </c>
       <c r="G1515" t="n">
-        <v>313.5</v>
+        <v>320.8500061035156</v>
       </c>
       <c r="H1515" t="n">
-        <v>3854</v>
+        <v>10446</v>
       </c>
       <c r="I1515" t="n">
-        <v>-2.4276340147248</v>
+        <v>-0.1400503288357058</v>
       </c>
       <c r="J1515" t="n">
-        <v>0.8272048992720072</v>
+        <v>0.8200327152043003</v>
       </c>
       <c r="K1515" t="n">
-        <v>-0.2857142757811482</v>
+        <v>-0.2689678501586198</v>
       </c>
       <c r="L1515" t="n">
-        <v>-0.2748930367195598</v>
+        <v>-0.2578929071954357</v>
       </c>
       <c r="M1515" t="n">
-        <v>288.8890017700195</v>
+        <v>289.0360018920899</v>
       </c>
       <c r="N1515" t="n">
-        <v>332.0622504425049</v>
+        <v>332.0990004730224</v>
       </c>
       <c r="O1515" t="inlineStr">
         <is>
@@ -85160,7 +85160,7 @@
         <v>46220</v>
       </c>
       <c r="B695" t="n">
-        <v>0.02821817811581392</v>
+        <v>0.0330008745300249</v>
       </c>
     </row>
   </sheetData>
@@ -85299,19 +85299,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>313.5</v>
+        <v>320.85</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.43</v>
+        <v>-0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>82.7</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
-        <v>-28.6</v>
+        <v>-26.9</v>
       </c>
       <c r="L2" t="n">
-        <v>-27.5</v>
+        <v>-25.8</v>
       </c>
       <c r="M2" t="n">
         <v>432.35</v>
@@ -85325,7 +85325,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>117562</v>
+        <v>120319</v>
       </c>
       <c r="Q2" t="n">
         <v>0.03</v>

--- a/commodity-risk-dashboard/data/commodities_powerbi.xlsx
+++ b/commodity-risk-dashboard/data/commodities_powerbi.xlsx
@@ -40013,28 +40013,28 @@
         <v>79.75</v>
       </c>
       <c r="G758" t="n">
-        <v>78.43000030517578</v>
+        <v>78.93000030517578</v>
       </c>
       <c r="H758" t="n">
-        <v>12025</v>
+        <v>20908</v>
       </c>
       <c r="I758" t="n">
-        <v>0.9525007600915458</v>
+        <v>1.596084212643367</v>
       </c>
       <c r="J758" t="n">
-        <v>0.3358566007371769</v>
+        <v>0.3383230397922864</v>
       </c>
       <c r="K758" t="n">
-        <v>-0.2390608272300767</v>
+        <v>-0.2342097551287822</v>
       </c>
       <c r="L758" t="n">
-        <v>-0.1064144547694758</v>
+        <v>-0.1007177472484153</v>
       </c>
       <c r="M758" t="n">
-        <v>77.23340026855469</v>
+        <v>77.24340026855469</v>
       </c>
       <c r="N758" t="n">
-        <v>68.7234001159668</v>
+        <v>68.72590011596679</v>
       </c>
       <c r="O758" t="inlineStr">
         <is>
@@ -79559,7 +79559,7 @@
         <v>320.8500061035156</v>
       </c>
       <c r="H1515" t="n">
-        <v>10446</v>
+        <v>12399</v>
       </c>
       <c r="I1515" t="n">
         <v>-0.1400503288357058</v>
@@ -85160,7 +85160,7 @@
         <v>46220</v>
       </c>
       <c r="B695" t="n">
-        <v>0.0330008745300249</v>
+        <v>0.03242065832047512</v>
       </c>
     </row>
   </sheetData>
@@ -85366,19 +85366,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>78.43000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-23.9</v>
+        <v>-23.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-10.6</v>
+        <v>-10.1</v>
       </c>
       <c r="M3" t="n">
         <v>87.77</v>
@@ -85392,7 +85392,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>39215</v>
+        <v>39465</v>
       </c>
       <c r="Q3" t="n">
         <v>0.03</v>
